--- a/WikiViewer Documents/planning_poker.xlsx
+++ b/WikiViewer Documents/planning_poker.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vikol\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aris\Desktop\ΠΛΗ24\ΓΕ\ΓΕ3\WikiViewer Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25C4A90-7686-45B7-9C21-5A63D015F242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCFE6CBC-F024-4A92-83DE-A75E53253FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planning Poker" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -162,9 +165,6 @@
     <t>Priority Poker</t>
   </si>
   <si>
-    <t>Screenshots - User Guide (6 screenshots)</t>
-  </si>
-  <si>
     <t>Video - Παρουσίαση 15 λεπτών</t>
   </si>
   <si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>6. Μπλε κείμενο = Αρχικά Story Points από το CSV</t>
+  </si>
+  <si>
+    <t>Screenshots - User Guide</t>
   </si>
 </sst>
 </file>
@@ -245,7 +248,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -268,11 +271,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -290,6 +306,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -554,8 +571,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J42"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="70" customWidth="1"/>
@@ -563,7 +580,7 @@
     <col min="4" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -595,7 +612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="4"/>
       <c r="B2" s="4" t="s">
         <v>10</v>
@@ -609,12 +626,12 @@
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
       <c r="I2" s="6" t="str">
-        <f t="shared" ref="I2:I33" si="0">IF(COUNTA(D2:H2)=0,"",AVERAGE(D2:H2))</f>
+        <f t="shared" ref="I2:I34" si="0">IF(COUNTA(D2:H2)=0,"",AVERAGE(D2:H2))</f>
         <v/>
       </c>
       <c r="J2" s="6"/>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="4" t="s">
         <v>12</v>
@@ -633,7 +650,7 @@
       </c>
       <c r="J3" s="6"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="4"/>
       <c r="B4" s="4" t="s">
         <v>14</v>
@@ -652,7 +669,7 @@
       </c>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="4"/>
       <c r="B5" s="4" t="s">
         <v>16</v>
@@ -671,7 +688,7 @@
       </c>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="4"/>
       <c r="B6" s="4" t="s">
         <v>18</v>
@@ -690,7 +707,7 @@
       </c>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
       <c r="B7" s="4" t="s">
         <v>20</v>
@@ -709,7 +726,7 @@
       </c>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="4"/>
       <c r="B8" s="4" t="s">
         <v>21</v>
@@ -728,7 +745,7 @@
       </c>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="4"/>
       <c r="B9" s="4" t="s">
         <v>22</v>
@@ -747,7 +764,7 @@
       </c>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="4"/>
       <c r="B10" s="4" t="s">
         <v>23</v>
@@ -766,7 +783,7 @@
       </c>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
       <c r="B11" s="4" t="s">
         <v>24</v>
@@ -785,7 +802,7 @@
       </c>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>25</v>
@@ -804,7 +821,7 @@
       </c>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="4"/>
       <c r="B13" s="4" t="s">
         <v>26</v>
@@ -823,7 +840,7 @@
       </c>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="4"/>
       <c r="B14" s="4" t="s">
         <v>27</v>
@@ -842,7 +859,7 @@
       </c>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="4"/>
       <c r="B15" s="4" t="s">
         <v>28</v>
@@ -861,7 +878,7 @@
       </c>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="4"/>
       <c r="B16" s="4" t="s">
         <v>29</v>
@@ -880,7 +897,7 @@
       </c>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="4"/>
       <c r="B17" s="4" t="s">
         <v>30</v>
@@ -899,7 +916,7 @@
       </c>
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="4"/>
       <c r="B18" s="4" t="s">
         <v>31</v>
@@ -918,7 +935,7 @@
       </c>
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="4"/>
       <c r="B19" s="4" t="s">
         <v>32</v>
@@ -937,7 +954,7 @@
       </c>
       <c r="J19" s="6"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="4"/>
       <c r="B20" s="4" t="s">
         <v>33</v>
@@ -956,7 +973,7 @@
       </c>
       <c r="J20" s="6"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="4"/>
       <c r="B21" s="4" t="s">
         <v>34</v>
@@ -975,7 +992,7 @@
       </c>
       <c r="J21" s="6"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
       <c r="B22" s="4" t="s">
         <v>35</v>
@@ -994,7 +1011,7 @@
       </c>
       <c r="J22" s="6"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="4"/>
       <c r="B23" s="4" t="s">
         <v>36</v>
@@ -1013,7 +1030,7 @@
       </c>
       <c r="J23" s="6"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="4"/>
       <c r="B24" s="4" t="s">
         <v>37</v>
@@ -1032,7 +1049,7 @@
       </c>
       <c r="J24" s="6"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="4"/>
       <c r="B25" s="4" t="s">
         <v>38</v>
@@ -1051,7 +1068,7 @@
       </c>
       <c r="J25" s="6"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="4"/>
       <c r="B26" s="4" t="s">
         <v>39</v>
@@ -1070,7 +1087,7 @@
       </c>
       <c r="J26" s="6"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="4"/>
       <c r="B27" s="4" t="s">
         <v>40</v>
@@ -1089,7 +1106,7 @@
       </c>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="4"/>
       <c r="B28" s="4" t="s">
         <v>41</v>
@@ -1108,10 +1125,10 @@
       </c>
       <c r="J28" s="6"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="4"/>
       <c r="B29" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>13</v>
@@ -1127,10 +1144,10 @@
       </c>
       <c r="J29" s="6"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="4"/>
       <c r="B30" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>13</v>
@@ -1146,10 +1163,10 @@
       </c>
       <c r="J30" s="6"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="4"/>
       <c r="B31" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>11</v>
@@ -1165,10 +1182,10 @@
       </c>
       <c r="J31" s="6"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="4"/>
       <c r="B32" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>13</v>
@@ -1184,10 +1201,10 @@
       </c>
       <c r="J32" s="6"/>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="4"/>
       <c r="B33" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>13</v>
@@ -1203,37 +1220,42 @@
       </c>
       <c r="J33" s="6"/>
     </row>
-    <row r="35" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>47</v>
-      </c>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J34" s="6"/>
+    </row>
+    <row r="35" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="2"/>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>48</v>
+    </row>
+    <row r="36" spans="1:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1245,9 +1267,9 @@
       <c r="I37" s="1"/>
       <c r="J37" s="1"/>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1259,9 +1281,9 @@
       <c r="I38" s="1"/>
       <c r="J38" s="1"/>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1273,9 +1295,9 @@
       <c r="I39" s="1"/>
       <c r="J39" s="1"/>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -1287,9 +1309,9 @@
       <c r="I40" s="1"/>
       <c r="J40" s="1"/>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -1301,16 +1323,19 @@
       <c r="I41" s="1"/>
       <c r="J41" s="1"/>
     </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D42" s="1"/>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A35:J35"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A38:J38"/>
-    <mergeCell ref="A39:J39"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
